--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128633556</v>
+        <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460410</v>
+        <v>460408</v>
       </c>
       <c r="R2" t="n">
-        <v>6794513</v>
+        <v>6794579</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128635470</v>
+        <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460408</v>
+        <v>460410</v>
       </c>
       <c r="R3" t="n">
-        <v>6794579</v>
+        <v>6794513</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128635883</v>
+        <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79673</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460406</v>
+        <v>460415</v>
       </c>
       <c r="R4" t="n">
-        <v>6794539</v>
+        <v>6794621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +970,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 bild , stubbe med tallar i bakgrund</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128634891</v>
+        <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460415</v>
+        <v>460406</v>
       </c>
       <c r="R5" t="n">
-        <v>6794621</v>
+        <v>6794539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1077,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 bild , stubbe med tallar i bakgrund</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128635426</v>
+        <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460384</v>
+        <v>460376</v>
       </c>
       <c r="R8" t="n">
-        <v>6794590</v>
+        <v>6794580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128635355</v>
+        <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460376</v>
+        <v>460384</v>
       </c>
       <c r="R9" t="n">
-        <v>6794580</v>
+        <v>6794590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128633559</v>
+        <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460410</v>
+        <v>460385</v>
       </c>
       <c r="R11" t="n">
-        <v>6794513</v>
+        <v>6794602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128635165</v>
+        <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460385</v>
+        <v>460410</v>
       </c>
       <c r="R13" t="n">
-        <v>6794602</v>
+        <v>6794513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635470</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128633556</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128634891</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128635355</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128635426</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128635765</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128635165</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128634697</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128633559</v>
       </c>
       <c r="B13" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128635578</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39478-2025 artfynd.xlsx
+++ b/artfynd/A 39478-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128635883</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128634869</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128635417</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128633553</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
